--- a/SOURCES/SOURCE_SAISIES_PIECES.xlsx
+++ b/SOURCES/SOURCE_SAISIES_PIECES.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sazience-my.sharepoint.com/personal/marc_kassi_sazience_com/Documents/Projets internes/data_validator_app/LES_TABLES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sazience-my.sharepoint.com/personal/marc_kassi_sazience_com/Documents/Projets internes/data_validator_app/SOURCES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{88B1D843-1834-4AA4-AA87-781AE85D0837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AC9052E-0F5D-49A4-8316-13F7C4B666F9}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{88B1D843-1834-4AA4-AA87-781AE85D0837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61234D4F-138E-4691-BC9D-1EA03EDA3A48}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9E200972-4B03-4000-8C9B-356CDD63AE9C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="920">
   <si>
     <t>Comptes_comptables</t>
   </si>
@@ -2459,30 +2459,6 @@
     <t>FL0111</t>
   </si>
   <si>
-    <t>FL0110</t>
-  </si>
-  <si>
-    <t>FL0109</t>
-  </si>
-  <si>
-    <t>FL0108</t>
-  </si>
-  <si>
-    <t>FL0107</t>
-  </si>
-  <si>
-    <t>FL0106</t>
-  </si>
-  <si>
-    <t>FL0105</t>
-  </si>
-  <si>
-    <t>FL0102</t>
-  </si>
-  <si>
-    <t>FL0100</t>
-  </si>
-  <si>
     <t>Code_tiers</t>
   </si>
   <si>
@@ -2808,6 +2784,18 @@
   </si>
   <si>
     <t>AX207</t>
+  </si>
+  <si>
+    <t>FL-0160</t>
+  </si>
+  <si>
+    <t>FL-0161</t>
+  </si>
+  <si>
+    <t>FL-0162</t>
+  </si>
+  <si>
+    <t>FL-0163</t>
   </si>
 </sst>
 </file>
@@ -2831,7 +2819,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2839,14 +2827,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2863,6 +2865,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3196,27 +3202,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>102100</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>814</v>
+      <c r="B2" s="2" t="s">
+        <v>916</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -3224,13 +3230,13 @@
         <v>102200</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>813</v>
+        <v>917</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -3238,13 +3244,13 @@
         <v>102800</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>812</v>
+        <v>918</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -3252,13 +3258,13 @@
         <v>103000</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>811</v>
+        <v>919</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -3266,13 +3272,13 @@
         <v>104100</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -3280,13 +3286,13 @@
         <v>104200</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -3294,13 +3300,13 @@
         <v>104300</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -3308,13 +3314,13 @@
         <v>104700</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -3325,10 +3331,10 @@
         <v>806</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -3339,10 +3345,10 @@
         <v>805</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -3353,10 +3359,10 @@
         <v>804</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -3367,10 +3373,10 @@
         <v>803</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -3381,10 +3387,10 @@
         <v>802</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -3395,10 +3401,10 @@
         <v>801</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -3409,10 +3415,10 @@
         <v>800</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -3423,10 +3429,10 @@
         <v>799</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -3437,10 +3443,10 @@
         <v>798</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -3451,10 +3457,10 @@
         <v>797</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -3465,10 +3471,10 @@
         <v>796</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -3479,10 +3485,10 @@
         <v>795</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -3493,10 +3499,10 @@
         <v>794</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -3507,10 +3513,10 @@
         <v>793</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -3521,10 +3527,10 @@
         <v>792</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -3535,10 +3541,10 @@
         <v>791</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -3549,10 +3555,10 @@
         <v>790</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -3563,10 +3569,10 @@
         <v>789</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -3577,10 +3583,10 @@
         <v>788</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -3591,10 +3597,10 @@
         <v>787</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -3605,10 +3611,10 @@
         <v>786</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -3619,10 +3625,10 @@
         <v>785</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -3633,10 +3639,10 @@
         <v>784</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -3647,10 +3653,10 @@
         <v>783</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -3661,10 +3667,10 @@
         <v>782</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -3675,10 +3681,10 @@
         <v>781</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -3689,10 +3695,10 @@
         <v>780</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -3703,10 +3709,10 @@
         <v>779</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -3717,10 +3723,10 @@
         <v>778</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -3731,10 +3737,10 @@
         <v>777</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -3745,10 +3751,10 @@
         <v>776</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>897</v>
+        <v>889</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -3759,10 +3765,10 @@
         <v>775</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -3773,10 +3779,10 @@
         <v>774</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>899</v>
+        <v>891</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -3787,7 +3793,7 @@
         <v>773</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -3798,7 +3804,7 @@
         <v>772</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -3809,7 +3815,7 @@
         <v>771</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -3820,7 +3826,7 @@
         <v>770</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -3831,7 +3837,7 @@
         <v>769</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -3842,7 +3848,7 @@
         <v>768</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -3853,7 +3859,7 @@
         <v>767</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -3864,7 +3870,7 @@
         <v>766</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -3875,7 +3881,7 @@
         <v>765</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>908</v>
+        <v>900</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -3886,7 +3892,7 @@
         <v>764</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -3897,7 +3903,7 @@
         <v>763</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -3908,7 +3914,7 @@
         <v>762</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -3919,7 +3925,7 @@
         <v>761</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -3930,7 +3936,7 @@
         <v>760</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -3941,7 +3947,7 @@
         <v>759</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -3952,7 +3958,7 @@
         <v>758</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -3963,7 +3969,7 @@
         <v>757</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -3974,7 +3980,7 @@
         <v>756</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -3985,7 +3991,7 @@
         <v>755</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -3996,7 +4002,7 @@
         <v>754</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -4007,7 +4013,7 @@
         <v>753</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -4018,7 +4024,7 @@
         <v>752</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
@@ -4029,7 +4035,7 @@
         <v>751</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
@@ -4040,7 +4046,7 @@
         <v>750</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
